--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,14 +39,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00595959"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,9 +114,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -493,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -655,7 +643,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Trong group, boss @bot 'giao Long task ...' (Chat ID Telegram numeric) → bot phải resolve được id và gọi create_task không crash</t>
+          <t>Trong group, boss @bot 'giao Long task ...' (Chat ID Telegram numeric) → bot resolve được id và gọi create_task không crash</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -670,7 +658,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>FIXED — trước đây crash int(Chat ID); giờ chạy qua resolve_lark_chat_id</t>
+          <t>FIXED — round 1 đã thay int(Chat ID) bằng resolve_lark_chat_id</t>
         </is>
       </c>
     </row>
@@ -697,7 +685,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Trong group, boss @bot 'giao Hùng task ...' (Chat ID Zalo alphanum) → bot phải resolve được id và gọi create_task không crash</t>
+          <t>Trong group, boss @bot 'giao Hùng task ...' (Chat ID Zalo alphanum) → bot resolve được id và gọi create_task không crash</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -712,7 +700,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>FIXED — đây là regression test mới riêng cho Zalo</t>
+          <t>FIXED — regression test riêng cho Zalo</t>
         </is>
       </c>
     </row>
@@ -744,7 +732,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>DM tạo reminder cho chính boss</t>
+          <t>DM: self-reminder</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -786,12 +774,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Group @mention tạo reminder cho 1 member</t>
+          <t>Group @mention: nhắc 1 member cụ thể</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Trong group, boss @bot 'nhắc Long ...' → bot tạo reminder với target=member, source_chat_id=group</t>
+          <t>Trong group, boss @bot 'nhắc Long ...' → bot tạo reminder target=member, source_chat_id=group</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -833,7 +821,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Gọi send_reminder(reminder dict có target_chat_id) trực tiếp → bot gửi DM tới target</t>
+          <t>Gọi send_reminder(target_chat_id) trực tiếp → bot gửi DM tới target</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -848,7 +836,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Bypass scheduler để test logic dispatch riêng</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -870,27 +858,27 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Source recognition khi fire</t>
+          <t>Fire reminder source-only (không target, có source)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Khi reminder fire, message tới target phải reference đúng source group / boss</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>NOT_TESTED</t>
+          <t>Reminder không có target_chat_id, có source_chat_id → bot gửi outbound vào source group thay vì DM boss</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>outbound vào source group</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Cần extend R3 thêm assertion về nội dung message</t>
+          <t>Verify _destination_for routing logic</t>
         </is>
       </c>
     </row>
@@ -937,7 +925,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>tool append_note + set_language được gọi</t>
+          <t>tool append_note / update_note được gọi</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -964,7 +952,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok</t>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -979,7 +967,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Boss gửi file .txt + 'tóm tắt giúp tôi' → bot ingest file và phản hồi nội dung</t>
+          <t>Boss gửi file .txt + 'tóm tắt' → bot phải reference keyword đặc trưng (zulipix/qorantek) HOẶC disclaim honest về không hỗ trợ .txt</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -989,12 +977,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>reply &gt; 30 chars</t>
+          <t>bot disclaim 'chưa đọc trực tiếp file .txt'</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Weak check — chỉ verify reply không rỗng, chưa verify nội dung đúng</t>
+          <t>Feature gap đã document: file_ingestion chưa support text/plain (chỉ image/PDF/DOCX). Bot honest về điều này.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +994,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok</t>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1021,7 +1009,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Boss gửi 'xem video này: https://youtube.com/...' → bot xử lý URL, phản hồi có nội dung</t>
+          <t>Boss gửi YouTube link → bot phải hoặc gọi web_search HOẶC disclaim honest, KHÔNG hallucinate nội dung video</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1031,12 +1019,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>reply &gt; 30 chars</t>
+          <t>bot disclaim 'chưa thể mở trực tiếp video YouTube'</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Weak check — bot có thể chưa thực sự fetch video; chỉ test không crash</t>
+          <t>Behavior đúng — bot không có URL fetcher cho video</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1036,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok</t>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1063,7 +1051,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Boss gửi 'video này nội dung gì: https://tiktok.com/...' → bot phản hồi</t>
+          <t>Boss gửi TikTok link → tương tự F2</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1073,200 +1061,284 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>reply &gt; 20 chars</t>
+          <t>bot disclaim 'không mở trực tiếp video TikTok'</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Weak check như F2</t>
+          <t>Behavior đúng</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>DM paste link bài báo (vnexpress)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Boss gửi link tin tức → bot nên gọi web_search để lấy info; nếu không thì disclaim</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>tool web_search được gọi</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Bot ưu tiên web_search cho URL có domain bài báo</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Image attachment (PNG 32x32 đỏ)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply reference khái niệm ảnh/màu</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>reply nhắc tới ảnh / màu</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>File ingestion path qua LOCAL_IMAGE sentinel + OpenAI Vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Onboard</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Khả năng hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Hỏi boss / xin phép khi có người mới</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>O1</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>New-member event trong group đã onboarded</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Sự kiện 'có người mới vào group' → bot phải reply (chào hoặc hỏi boss confirm)</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>no outbound at all</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Test setup chưa kích hoạt đúng nhánh group_onboarding; cần verify behavior expected trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Onboard</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Khả năng hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Stranger DM xin vào workspace → boss approve</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>User lạ DM bot → bot ask which workspace → request_join tới boss → boss approve_join → user được activate</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>NOT_TESTED</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Cần multi-actor scenario (stranger + boss); chưa build</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>New-member event trong group đã onboarded — silent expected</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Telegram emit service event 'X joined the group' → bot KHÔNG tự reply (chỉ passive identity harvest). Verify silence.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>no replies, no outbound</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Re-framed test: silence là correct behavior. Boss-approval đi qua O2 (DM).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Onboard</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Hỏi boss / xin phép khi có người mới</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Boss duyệt pending member</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Pre-insert pending membership → boss DM 'duyệt' → bot gọi approve_join → membership chuyển active</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>tool approve_join + membership.status='active'</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Test gateway approve_join service; chưa cover full LLM-driven request_join path (stranger DM full onboarding flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Bot tự báo sếp khi member im lặng / quá hạn</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Task overdue → bot DM assignee + báo sếp</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Inject task có Deadline trong quá khứ vào Lark stub → gọi _after_deadline_check → bot gửi outbound</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Inject task có Deadline trong quá khứ → _after_deadline_check → outbound</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>outbound triggered</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>FIXED — int(Chat ID) ở scheduler:223 đã được resolve_lark_chat_id thay thế</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>FIXED — int(Chat ID) ở scheduler:223 đã được resolver thay thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Bot tự báo sếp khi member im lặng / quá hạn</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Member bị nhắc deadline không reply → bot báo sếp</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Reminder fire → target nhận DM → target không reply trong N phút → bot tự DM boss</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>NOT_TESTED</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Reminder fire → target im lặng N phút → bot tự DM boss</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>FEATURE_GAP</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Cần timer-based simulation, chưa build</t>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Không có timer-based no-reply escalation cho reminder trong code (chỉ có cho task deadline). Cần feature mới nếu muốn.</t>
         </is>
       </c>
     </row>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,10 +39,23 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00595959"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -51,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +79,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,9 +124,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,7 +162,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -494,663 +543,473 @@
     <col width="56" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cluster_purpose</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>case_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>case_intent</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>SMART bot — self-test summary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Generated</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>DM tạo task</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Boss DM bot 'tạo task ...' → bot gọi create_task</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>tool create_task được gọi</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>2026-05-14 10:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Total cases</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>DM liệt kê task</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Boss DM 'cho xem danh sách task' → bot gọi list_tasks</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>tool list_tasks được gọi</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>T3a</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Group @mention giao task cho người Telegram</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Trong group, boss @bot 'giao Long task ...' (Chat ID Telegram numeric) → bot resolve được id và gọi create_task không crash</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>tool create_task không lỗi</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>FIXED — round 1 đã thay int(Chat ID) bằng resolve_lark_chat_id</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>T3b</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Group @mention giao task cho người Zalo</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Trong group, boss @bot 'giao Hùng task ...' (Chat ID Zalo alphanum) → bot resolve được id và gọi create_task không crash</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>tool create_task không lỗi</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>FIXED — regression test riêng cho Zalo</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_TESTED</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>FEATURE_GAP</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>cluster_purpose</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>case_name</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>case_intent</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>DM tạo task</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Boss DM bot 'tạo task ...' → bot gọi create_task</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>tool create_task được gọi</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>DM liệt kê task</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Boss DM 'cho xem danh sách task' → bot gọi list_tasks</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>tool list_tasks được gọi</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>T3a</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Group @mention giao task cho người Telegram</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Trong group, boss @bot 'giao Long task ...' (Chat ID Telegram numeric) → bot resolve được id và gọi create_task không crash</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>tool create_task không lỗi</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — round 1 đã thay int(Chat ID) bằng resolve_lark_chat_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>T3b</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Group @mention giao task cho người Zalo</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Trong group, boss @bot 'giao Hùng task ...' (Chat ID Zalo alphanum) → bot resolve được id và gọi create_task không crash</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>tool create_task không lỗi</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — regression test riêng cho Zalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Tạo / fire / nhận diện nguồn reminder</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>DM: self-reminder</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Boss DM 'nhắc tôi ...' → bot gọi create_reminder với target = boss</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>tool create_reminder được gọi</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Tạo / fire / nhận diện nguồn reminder</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Group @mention: nhắc 1 member cụ thể</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Trong group, boss @bot 'nhắc Long ...' → bot tạo reminder target=member, source_chat_id=group</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>tool create_reminder được gọi</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Tạo / fire / nhận diện nguồn reminder</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Fire reminder trực tiếp (bypass scheduler)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Gọi send_reminder(target_chat_id) trực tiếp → bot gửi DM tới target</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>outbound tới target_chat_id</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Tạo / fire / nhận diện nguồn reminder</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Fire reminder source-only (không target, có source)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Reminder không có target_chat_id, có source_chat_id → bot gửi outbound vào source group thay vì DM boss</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>outbound vào source group</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Verify _destination_for routing logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Khả năng auto-take note từ hội thoại tự nhiên</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>N1</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Auto-append khi boss chia sẻ context cá nhân</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Boss nói 'gọi tôi là anh Đạt, thích phong cách ngắn gọn' → bot gọi append_note / update_note</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>tool append_note / update_note được gọi</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>File-Link</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>DM gửi text file kèm caption</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Boss gửi file .txt + 'tóm tắt' → bot phải reference keyword đặc trưng (zulipix/qorantek) HOẶC disclaim honest về không hỗ trợ .txt</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>bot disclaim 'chưa đọc trực tiếp file .txt'</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Feature gap đã document: file_ingestion chưa support text/plain (chỉ image/PDF/DOCX). Bot honest về điều này.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>File-Link</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>DM paste link YouTube</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Boss gửi YouTube link → bot phải hoặc gọi web_search HOẶC disclaim honest, KHÔNG hallucinate nội dung video</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>bot disclaim 'chưa thể mở trực tiếp video YouTube'</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Behavior đúng — bot không có URL fetcher cho video</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>File-Link</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>DM paste link TikTok</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Boss gửi TikTok link → tương tự F2</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>bot disclaim 'không mở trực tiếp video TikTok'</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Behavior đúng</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>File-Link</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>DM paste link bài báo (vnexpress)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Boss gửi link tin tức → bot nên gọi web_search để lấy info; nếu không thì disclaim</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>tool web_search được gọi</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Bot ưu tiên web_search cho URL có domain bài báo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>File-Link</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Image attachment (PNG 32x32 đỏ)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply reference khái niệm ảnh/màu</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>reply nhắc tới ảnh / màu</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>File ingestion path qua LOCAL_IMAGE sentinel + OpenAI Vision</t>
         </is>
       </c>
     </row>
@@ -1165,184 +1024,459 @@
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Khả năng auto-take note từ hội thoại tự nhiên</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Auto-append khi boss chia sẻ context cá nhân</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Boss nói 'gọi tôi là anh Đạt, thích phong cách ngắn gọn' → bot gọi append_note / update_note</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>tool append_note / update_note được gọi</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>DM gửi text file kèm caption</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Boss gửi file .txt + 'tóm tắt' → bot phải reference keyword đặc trưng (zulipix/qorantek) HOẶC disclaim honest về không hỗ trợ .txt</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>bot disclaim 'chưa đọc trực tiếp file .txt'</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Feature gap đã document: file_ingestion chưa support text/plain (chỉ image/PDF/DOCX). Bot honest về điều này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>DM paste link YouTube</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Boss gửi YouTube link → bot phải hoặc gọi web_search HOẶC disclaim honest, KHÔNG hallucinate nội dung video</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>bot disclaim 'chưa thể mở trực tiếp video YouTube'</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Behavior đúng — bot không có URL fetcher cho video</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>DM paste link TikTok</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Boss gửi TikTok link → tương tự F2</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>bot disclaim 'không mở trực tiếp video TikTok'</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Behavior đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>DM paste link bài báo (vnexpress)</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Boss gửi link tin tức → bot nên gọi web_search để lấy info; nếu không thì disclaim</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>tool web_search được gọi</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Bot ưu tiên web_search cho URL có domain bài báo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Image attachment (PNG 32x32 đỏ)</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply reference khái niệm ảnh/màu</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>reply nhắc tới ảnh / màu</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>File ingestion path qua LOCAL_IMAGE sentinel + OpenAI Vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Onboard</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Hỏi boss / xin phép khi có người mới</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>O1</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>New-member event trong group đã onboarded — silent expected</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Telegram emit service event 'X joined the group' → bot KHÔNG tự reply (chỉ passive identity harvest). Verify silence.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>no replies, no outbound</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>Re-framed test: silence là correct behavior. Boss-approval đi qua O2 (DM).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Onboard</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Hỏi boss / xin phép khi có người mới</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Boss duyệt pending member</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Pre-insert pending membership → boss DM 'duyệt' → bot gọi approve_join → membership chuyển active</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>tool approve_join + membership.status='active'</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>Test gateway approve_join service; chưa cover full LLM-driven request_join path (stranger DM full onboarding flow)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Bot tự báo sếp khi member im lặng / quá hạn</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Task overdue → bot DM assignee + báo sếp</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Inject task có Deadline trong quá khứ → _after_deadline_check → outbound</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>outbound triggered</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>FIXED — int(Chat ID) ở scheduler:223 đã được resolver thay thế</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Bot tự báo sếp khi member im lặng / quá hạn</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Member bị nhắc deadline không reply → bot báo sếp</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Reminder fire → target im lặng N phút → bot tự DM boss</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>FEATURE_GAP</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>Không có timer-based no-reply escalation cho reminder trong code (chỉ có cho task deadline). Cần feature mới nếu muốn.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 10:49</t>
+          <t>2026-05-14 10:57</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi file .txt + 'tóm tắt' → bot phải reference keyword đặc trưng (zulipix/qorantek) HOẶC disclaim honest về không hỗ trợ .txt</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Boss gửi file .txt + 'tóm tắt' → bot phải đọc nội dung (reply có keyword đặc trưng zulipix/qorantek)</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>FEATURE_GAP</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Feature gap đã document: file_ingestion chưa support text/plain (chỉ image/PDF/DOCX). Bot honest về điều này.</t>
+          <t>file_ingestion chưa support text/plain — cần thêm handler đọc UTF-8 plain text (chỉ ~5 dòng code: read + return content)</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi YouTube link → bot phải hoặc gọi web_search HOẶC disclaim honest, KHÔNG hallucinate nội dung video</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Boss gửi YouTube link → bot phải fetch transcript / oEmbed / web_search để nắm nội dung</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>FEATURE_GAP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Behavior đúng — bot không có URL fetcher cho video</t>
+          <t>Không có YouTube fetcher; cần tool mới (youtube_transcript_api / yt-dlp) hoặc dùng web_search như fallback</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi TikTok link → tương tự F2</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Boss gửi TikTok link → bot phải fetch metadata / scrape oEmbed</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>FEATURE_GAP</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Behavior đúng</t>
+          <t>Không có TikTok fetcher; TikTok oEmbed cho metadata; transcript khó hơn</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi link tin tức → bot nên gọi web_search để lấy info; nếu không thì disclaim</t>
+          <t>Boss gửi link tin tức → bot nên gọi web_search để lấy info</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Bot ưu tiên web_search cho URL có domain bài báo</t>
+          <t>Bot tự ưu tiên web_search cho URL có domain bài báo — feature hoạt động</t>
         </is>
       </c>
     </row>
@@ -1313,27 +1313,27 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>New-member event trong group đã onboarded — silent expected</t>
+          <t>New-member event trong group → bot phải hỏi boss</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Telegram emit service event 'X joined the group' → bot KHÔNG tự reply (chỉ passive identity harvest). Verify silence.</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Khi có người mới vào group đã onboarded, bot phải chủ động hỏi sếp (vd 'Có A vừa vào group X, có muốn thêm vào team không?')</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>FEATURE_GAP</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>no replies, no outbound</t>
+          <t>silent — bot không proactive hỏi boss</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Re-framed test: silence là correct behavior. Boss-approval đi qua O2 (DM).</t>
+          <t>Bot chỉ chạy passive identity.harvest, chưa có handler proactive cho new_member event. Cần thêm logic trong secretary_agent hoặc group flow.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Test gateway approve_join service; chưa cover full LLM-driven request_join path (stranger DM full onboarding flow)</t>
+          <t>Test gateway approve_join; chưa cover full LLM-driven request_join path (stranger DM full onboarding)</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Không có timer-based no-reply escalation cho reminder trong code (chỉ có cho task deadline). Cần feature mới nếu muốn.</t>
+          <t>Không có timer-based no-reply escalation cho reminder trong code (chỉ có cho task deadline). Cần feature mới.</t>
         </is>
       </c>
     </row>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 10:57</t>
+          <t>2026-05-14 11:13</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Group @mention giao task cho người Telegram</t>
+          <t>Group @mention giao task — Telegram assignee</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Trong group, boss @bot 'giao Long task ...' (Chat ID Telegram numeric) → bot resolve được id và gọi create_task không crash</t>
+          <t>Trong group, boss @bot 'giao Long task' (Chat ID Telegram numeric) → resolve được id, create_task không crash</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>FIXED — round 1 đã thay int(Chat ID) bằng resolve_lark_chat_id</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Group @mention giao task cho người Zalo</t>
+          <t>Group @mention giao task — Zalo assignee</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Trong group, boss @bot 'giao Hùng task ...' (Chat ID Zalo alphanum) → bot resolve được id và gọi create_task không crash</t>
+          <t>Trong group, boss @bot 'giao Hùng task' (Chat ID Zalo alphanum) → resolve được id, create_task không crash</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>FIXED — regression test riêng cho Zalo</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Boss DM 'nhắc tôi ...' → bot gọi create_reminder với target = boss</t>
+          <t>Boss DM 'nhắc tôi ...' → tool create_reminder với target=boss</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Group @mention: nhắc 1 member cụ thể</t>
+          <t>Group @mention nhắc 1 member</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Trong group, boss @bot 'nhắc Long ...' → bot tạo reminder target=member, source_chat_id=group</t>
+          <t>Trong group, boss @bot 'nhắc Long' → create_reminder với target=member, source_chat_id=group</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Fire reminder trực tiếp (bypass scheduler)</t>
+          <t>Fire reminder bypass scheduler</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Gọi send_reminder(target_chat_id) trực tiếp → bot gửi DM tới target</t>
+          <t>send_reminder(target_chat_id) trực tiếp → DM tới target</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Fire reminder source-only (không target, có source)</t>
+          <t>Fire reminder source-only</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Reminder không có target_chat_id, có source_chat_id → bot gửi outbound vào source group thay vì DM boss</t>
+          <t>Reminder không có target_chat_id, có source_chat_id → outbound vào source group thay vì DM boss</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Boss nói 'gọi tôi là anh Đạt, thích phong cách ngắn gọn' → bot gọi append_note / update_note</t>
+          <t>Boss nói 'gọi tôi là anh Đạt' → bot append_note / update_note</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>DM gửi text file kèm caption</t>
+          <t>DM gửi file text + caption</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi file .txt + 'tóm tắt' → bot phải đọc nội dung (reply có keyword đặc trưng zulipix/qorantek)</t>
+          <t>Boss gửi .txt + 'tóm tắt' → bot phải đọc nội dung file (keyword đặc trưng zulipix/qorantek phải xuất hiện)</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>file_ingestion chưa support text/plain — cần thêm handler đọc UTF-8 plain text (chỉ ~5 dòng code: read + return content)</t>
+          <t>file_ingestion chưa support text/plain. Cần thêm handler ~5 dòng: read UTF-8, return content</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi YouTube link → bot phải fetch transcript / oEmbed / web_search để nắm nội dung</t>
+          <t>Boss gửi YouTube link → bot phải fetch transcript / oEmbed / web_search</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>bot disclaim 'chưa thể mở trực tiếp video YouTube'</t>
+          <t>bot disclaim 'chưa thể mở trực tiếp video'</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Không có YouTube fetcher; cần tool mới (youtube_transcript_api / yt-dlp) hoặc dùng web_search như fallback</t>
+          <t>Không có YouTube fetcher; cần youtube_transcript_api / yt-dlp hoặc fallback web_search</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi TikTok link → bot phải fetch metadata / scrape oEmbed</t>
+          <t>Boss gửi TikTok link → bot phải fetch metadata / oEmbed</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>bot disclaim 'không mở trực tiếp video TikTok'</t>
+          <t>bot disclaim 'không mở trực tiếp video'</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Không có TikTok fetcher; TikTok oEmbed cho metadata; transcript khó hơn</t>
+          <t>Không có TikTok fetcher</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi link tin tức → bot nên gọi web_search để lấy info</t>
+          <t>Boss gửi link tin tức → bot phải web_search để fetch</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Bot tự ưu tiên web_search cho URL có domain bài báo — feature hoạt động</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply reference khái niệm ảnh/màu</t>
+          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply nhắc ảnh/màu</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>File ingestion path qua LOCAL_IMAGE sentinel + OpenAI Vision</t>
+          <t>File ingestion → LOCAL_IMAGE sentinel + OpenAI Vision</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>New-member event trong group → bot phải hỏi boss</t>
+          <t>New-member event group đã onboarded → bot phải hỏi boss</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Khi có người mới vào group đã onboarded, bot phải chủ động hỏi sếp (vd 'Có A vừa vào group X, có muốn thêm vào team không?')</t>
+          <t>Người mới vào group đã onboarded → bot proactive hỏi sếp về thêm vào team</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>silent — bot không proactive hỏi boss</t>
+          <t>silent — bot không proactive</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Bot chỉ chạy passive identity.harvest, chưa có handler proactive cho new_member event. Cần thêm logic trong secretary_agent hoặc group flow.</t>
+          <t>Bot chỉ chạy passive identity.harvest. Cần handler proactive khi new_members non-empty + group đã onboarded</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Pre-insert pending membership → boss DM 'duyệt' → bot gọi approve_join → membership chuyển active</t>
+          <t>Pre-insert pending membership → boss DM 'duyệt' → approve_join → membership active</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Test gateway approve_join; chưa cover full LLM-driven request_join path (stranger DM full onboarding)</t>
+          <t>Cover gateway approve_join service</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp khi member im lặng / quá hạn</t>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Task overdue → bot DM assignee + báo sếp</t>
+          <t>Task overdue (DM context) → assignee DM + boss report</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Inject task có Deadline trong quá khứ → _after_deadline_check → outbound</t>
+          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>outbound triggered</t>
+          <t>outbound tới assignee DM + boss conv</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>FIXED — int(Chat ID) ở scheduler:223 đã được resolver thay thế</t>
+          <t>FIXED — strengthened: kiểm tra cả 2 outbound destination</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp khi member im lặng / quá hạn</t>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -1469,7 +1469,49 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Không có timer-based no-reply escalation cho reminder trong code (chỉ có cho task deadline). Cần feature mới.</t>
+          <t>Không có timer-based no-reply escalation cho reminder. Cần feature mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Task từ group, assignee chưa join → reminder vào group</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group thay vì silent</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>outbound vào source group</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — _resolve_task_targets helper trong scheduler; route theo Group ID khi present</t>
         </is>
       </c>
     </row>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 11:13</t>
+          <t>2026-05-14 11:25</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1101,19 +1101,19 @@
           <t>Boss gửi .txt + 'tóm tắt' → bot phải đọc nội dung file (keyword đặc trưng zulipix/qorantek phải xuất hiện)</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>FEATURE_GAP</t>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>bot disclaim 'chưa đọc trực tiếp file .txt'</t>
+          <t>bot đọc và reference keyword từ file</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>file_ingestion chưa support text/plain. Cần thêm handler ~5 dòng: read UTF-8, return content</t>
+          <t>FIXED — _ingest_text handler đọc text/plain + .txt/.md/.log/.csv/.json/.yaml/.ini/.conf (đặc biệt quan trọng cho Zalo vì bridge thường drop mime)</t>
         </is>
       </c>
     </row>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 11:25</t>
+          <t>2026-05-14 11:31</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1380,136 +1380,230 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Onboard</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Hỏi boss / xin phép khi có người mới</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Stranger gọi request_join → pending row + boss được DM</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Stranger gọi service request_join → membership pending tạo + boss nhận outbound (qua channel của boss qua _messenger_for)</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>membership status=pending + outbound to boss conv</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Test phần TRƯỚC của join flow (phần SAU = O2). Full path stranger DM → onboarding LLM → request_join chưa test end-to-end vì phụ thuộc LLM extract.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Escalation</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Task overdue (DM context) → assignee DM + boss report</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>outbound tới assignee DM + boss conv</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — strengthened: kiểm tra cả 2 outbound destination</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Cross-channel isolation rules</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Boss Zalo chỉ giao tiếp với người Zalo (channel isolation)</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Boss đăng ký Zalo → outbound đến contact phải qua kênh Zalo. Nếu contact chỉ có Telegram identity → bot phải skip / fallback / warn, không lén route qua Telegram</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>FEATURE_GAP</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Code hiện không có `bosses.primary_channel`. _messenger_for chọn theo provider của conversation đích, không biết boss đang ở đâu. Cần: (1) thêm column primary_channel set lúc onboard, (2) check trước outbound, (3) cảnh báo khi add_people khác channel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Bot tự báo sếp / route reminder khi quá hạn</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Task overdue (DM context) → assignee DM + boss report</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>outbound tới assignee DM + boss conv</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — strengthened: kiểm tra cả 2 outbound destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Member bị nhắc deadline không reply → bot báo sếp</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Reminder fire → target im lặng N phút → bot tự DM boss</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>FEATURE_GAP</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Không có timer-based no-reply escalation cho reminder. Cần feature mới.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Bot tự báo sếp / route reminder khi quá hạn</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Task từ group, assignee chưa join → reminder vào group</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group thay vì silent</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>outbound vào source group</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>FIXED — _resolve_task_targets helper trong scheduler; route theo Group ID khi present</t>
         </is>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -160,9 +160,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +555,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 11:31</t>
+          <t>2026-05-14 14:40</t>
         </is>
       </c>
     </row>
@@ -582,7 +579,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -618,7 +615,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1006,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Verify _destination_for routing logic</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1105,12 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>bot đọc và reference keyword từ file</t>
+          <t>bot reference keyword zulipix/qorantek từ file</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>FIXED — _ingest_text handler đọc text/plain + .txt/.md/.log/.csv/.json/.yaml/.ini/.conf (đặc biệt quan trọng cho Zalo vì bridge thường drop mime)</t>
+          <t>FIXED — _ingest_text handler đọc text/plain (Zalo bridge thường drop mime)</t>
         </is>
       </c>
     </row>
@@ -1140,22 +1137,22 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi YouTube link → bot phải fetch transcript / oEmbed / web_search</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>FEATURE_GAP</t>
+          <t>Boss gửi YouTube link → bot fetch via oEmbed</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>bot disclaim 'chưa thể mở trực tiếp video'</t>
+          <t>tool fetch_url được gọi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Không có YouTube fetcher; cần youtube_transcript_api / yt-dlp hoặc fallback web_search</t>
+          <t>FIXED — fetch_url tool mới + url_fetch_service hit YouTube oEmbed</t>
         </is>
       </c>
     </row>
@@ -1182,22 +1179,22 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi TikTok link → bot phải fetch metadata / oEmbed</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>FEATURE_GAP</t>
+          <t>Boss gửi TikTok link → bot fetch via oEmbed</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>bot disclaim 'không mở trực tiếp video'</t>
+          <t>tool fetch_url được gọi</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Không có TikTok fetcher</t>
+          <t>FIXED — fetch_url tool</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1221,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi link tin tức → bot phải web_search để fetch</t>
+          <t>Boss gửi link tin tức → bot fetch HTML + summary</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -1234,12 +1231,12 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>tool web_search được gọi</t>
+          <t>tool fetch_url được gọi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Path generic HTML qua fetch_url (trước đây dùng web_search; giờ chính xác hơn)</t>
         </is>
       </c>
     </row>
@@ -1313,27 +1310,27 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>New-member event group đã onboarded → bot phải hỏi boss</t>
+          <t>New-member event trong group → bot phải hỏi boss</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Người mới vào group đã onboarded → bot proactive hỏi sếp về thêm vào team</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>FEATURE_GAP</t>
+          <t>Người mới vào group đã onboarded → bot proactive DM boss hỏi role</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>silent — bot không proactive</t>
+          <t>outbound tới boss có tên 'Người Mới'</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Bot chỉ chạy passive identity.harvest. Cần handler proactive khi new_members non-empty + group đã onboarded</t>
+          <t>FIXED — _notify_boss_new_members trong secretary_agent.handle_message (qua _messenger_for nên route đúng channel boss)</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1372,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Cover gateway approve_join service</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1399,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Stranger gọi service request_join → membership pending tạo + boss nhận outbound (qua channel của boss qua _messenger_for)</t>
+          <t>Stranger gọi service request_join → membership pending + boss nhận outbound</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -1417,7 +1414,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Test phần TRƯỚC của join flow (phần SAU = O2). Full path stranger DM → onboarding LLM → request_join chưa test end-to-end vì phụ thuộc LLM extract.</t>
+          <t>Test phần TRƯỚC của join flow</t>
         </is>
       </c>
     </row>
@@ -1434,54 +1431,86 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Escalation</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Cross-channel isolation rules</t>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Boss Zalo chỉ giao tiếp với người Zalo (channel isolation)</t>
+          <t>Task overdue (DM context) → assignee DM + boss report</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Boss đăng ký Zalo → outbound đến contact phải qua kênh Zalo. Nếu contact chỉ có Telegram identity → bot phải skip / fallback / warn, không lén route qua Telegram</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>FEATURE_GAP</t>
+          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
+          <t>outbound tới assignee DM + boss conv</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Code hiện không có `bosses.primary_channel`. _messenger_for chọn theo provider của conversation đích, không biết boss đang ở đâu. Cần: (1) thêm column primary_channel set lúc onboard, (2) check trước outbound, (3) cảnh báo khi add_people khác channel.</t>
-        </is>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Reminder fire 4h trước, target im lặng → _check_no_reply_reminders → bot DM boss</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>outbound nhắc boss về Long + escalated=1</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — _check_no_reply_reminders scheduler tick mới (30 phút) + outbound_messages.escalated column</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -1496,17 +1525,17 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Task overdue (DM context) → assignee DM + boss report</t>
+          <t>Task từ group, assignee chưa join → reminder vào group</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
+          <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -1516,81 +1545,49 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>outbound tới assignee DM + boss conv</t>
+          <t>outbound vào source group</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>FIXED — strengthened: kiểm tra cả 2 outbound destination</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Escalation</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Reminder fire → target im lặng N phút → bot tự DM boss</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>FEATURE_GAP</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>Không có timer-based no-reply escalation cho reminder. Cần feature mới.</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Escalation</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+          <t>Cross-channel isolation per boss</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Task từ group, assignee chưa join → reminder vào group</t>
+          <t>Boss Zalo + Telegram-only assignee → reminder vào group, KHÔNG DM cross-channel</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group thay vì silent</t>
+          <t>Boss có primary_channel='zalo', assignee chỉ có Telegram identity → reminder PHẢI vào group, KHÔNG được DM Long qua Telegram</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -1600,12 +1597,12 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>outbound vào source group</t>
+          <t>outbound vào group + KHÔNG outbound vào Long DM</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>FIXED — _resolve_task_targets helper trong scheduler; route theo Group ID khi present</t>
+          <t>FIXED — bosses.primary_channel column + is_target_on_boss_channel filter trong _resolve_task_targets</t>
         </is>
       </c>
     </row>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 14:40</t>
+          <t>2026-05-14 15:38</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Fire reminder bypass scheduler</t>
+          <t>Fire reminder có target + source group → 3 destinations</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>send_reminder(target_chat_id) trực tiếp → DM tới target</t>
+          <t>send_reminder(target_chat_id + source_chat_id) → target nhận DM + boss nhận cc + source group nhận public notice 'Vừa nhắc X: ...'</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>outbound tới target_chat_id</t>
+          <t>3 outbound: target DM, boss cc, source group</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FIXED — reminder_agent.send_reminder giờ post thêm notice vào source group khi reminder được tạo trong group context</t>
         </is>
       </c>
     </row>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 15:38</t>
+          <t>2026-05-14 15:43</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1011,39 +1011,71 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Reminder</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Tạo / fire / nhận diện nguồn reminder</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Fire DM-only self-reminder → chỉ boss</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Self-reminder trong DM (target=None, source=None) → fire chỉ DM boss; KHÔNG group, KHÔNG DM người khác</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>outbound chỉ tới boss conv</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Đảm bảo nhắc lẻ không bị leak ra group / contact khác</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Reminder</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Khả năng auto-take note từ hội thoại tự nhiên</t>
+          <t>Tạo / fire / nhận diện nguồn reminder</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Auto-append khi boss chia sẻ context cá nhân</t>
+          <t>Fire DM-only target reminder → DM target + boss, KHÔNG group</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Boss nói 'gọi tôi là anh Đạt' → bot append_note / update_note</t>
+          <t>Boss DM tạo reminder cho Long (target có, source=None) → fire DM Long + cc boss; group KHÔNG có post</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -1053,12 +1085,12 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>tool append_note / update_note được gọi</t>
+          <t>outbound tới target DM + boss; group conv không có</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bảo đảm boss DM riêng → fire không lén post vào group</t>
         </is>
       </c>
     </row>
@@ -1075,27 +1107,27 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>File-Link</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+          <t>Khả năng auto-take note từ hội thoại tự nhiên</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>DM gửi file text + caption</t>
+          <t>Auto-append khi boss chia sẻ context cá nhân</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi .txt + 'tóm tắt' → bot phải đọc nội dung file (keyword đặc trưng zulipix/qorantek phải xuất hiện)</t>
+          <t>Boss nói 'gọi tôi là anh Đạt' → bot append_note / update_note</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -1105,56 +1137,24 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>bot reference keyword zulipix/qorantek từ file</t>
+          <t>tool append_note / update_note được gọi</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>FIXED — _ingest_text handler đọc text/plain (Zalo bridge thường drop mime)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>File-Link</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>DM paste link YouTube</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Boss gửi YouTube link → bot fetch via oEmbed</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>tool fetch_url được gọi</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — fetch_url tool mới + url_fetch_service hit YouTube oEmbed</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>DM paste link TikTok</t>
+          <t>DM gửi file text + caption</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi TikTok link → bot fetch via oEmbed</t>
+          <t>Boss gửi .txt + 'tóm tắt' → bot phải đọc nội dung file (keyword đặc trưng zulipix/qorantek phải xuất hiện)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>tool fetch_url được gọi</t>
+          <t>bot reference keyword zulipix/qorantek từ file</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>FIXED — fetch_url tool</t>
+          <t>FIXED — _ingest_text handler đọc text/plain (Zalo bridge thường drop mime)</t>
         </is>
       </c>
     </row>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>DM paste link bài báo (vnexpress)</t>
+          <t>DM paste link YouTube</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi link tin tức → bot fetch HTML + summary</t>
+          <t>Boss gửi YouTube link → bot fetch via oEmbed</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Path generic HTML qua fetch_url (trước đây dùng web_search; giờ chính xác hơn)</t>
+          <t>FIXED — fetch_url tool mới + url_fetch_service hit YouTube oEmbed</t>
         </is>
       </c>
     </row>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Image attachment (PNG 32x32 đỏ)</t>
+          <t>DM paste link TikTok</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply nhắc ảnh/màu</t>
+          <t>Boss gửi TikTok link → bot fetch via oEmbed</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -1273,49 +1273,81 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>reply nhắc tới ảnh / màu</t>
+          <t>tool fetch_url được gọi</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>File ingestion → LOCAL_IMAGE sentinel + OpenAI Vision</t>
+          <t>FIXED — fetch_url tool</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>File-Link</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>DM paste link bài báo (vnexpress)</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Boss gửi link tin tức → bot fetch HTML + summary</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>tool fetch_url được gọi</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Path generic HTML qua fetch_url (trước đây dùng web_search; giờ chính xác hơn)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Onboard</t>
+          <t>File-Link</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Hỏi boss / xin phép khi có người mới</t>
+          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>New-member event trong group → bot phải hỏi boss</t>
+          <t>Image attachment (PNG 32x32 đỏ)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Người mới vào group đã onboarded → bot proactive DM boss hỏi role</t>
+          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply nhắc ảnh/màu</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -1325,56 +1357,24 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>outbound tới boss có tên 'Người Mới'</t>
+          <t>reply nhắc tới ảnh / màu</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>FIXED — _notify_boss_new_members trong secretary_agent.handle_message (qua _messenger_for nên route đúng channel boss)</t>
+          <t>File ingestion → LOCAL_IMAGE sentinel + OpenAI Vision</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Onboard</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Boss duyệt pending member</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Pre-insert pending membership → boss DM 'duyệt' → approve_join → membership active</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>tool approve_join + membership.status='active'</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>O3</t>
+          <t>O1</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Stranger gọi request_join → pending row + boss được DM</t>
+          <t>New-member event trong group → bot phải hỏi boss</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Stranger gọi service request_join → membership pending + boss nhận outbound</t>
+          <t>Người mới vào group đã onboarded → bot proactive DM boss hỏi role</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -1409,49 +1409,81 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>membership status=pending + outbound to boss conv</t>
+          <t>outbound tới boss có tên 'Người Mới'</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Test phần TRƯỚC của join flow</t>
+          <t>FIXED — _notify_boss_new_members trong secretary_agent.handle_message (qua _messenger_for nên route đúng channel boss)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Onboard</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Hỏi boss / xin phép khi có người mới</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Boss duyệt pending member</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Pre-insert pending membership → boss DM 'duyệt' → approve_join → membership active</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>tool approve_join + membership.status='active'</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Escalation</t>
+          <t>Onboard</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+          <t>Hỏi boss / xin phép khi có người mới</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>O3</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Task overdue (DM context) → assignee DM + boss report</t>
+          <t>Stranger gọi request_join → pending row + boss được DM</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
+          <t>Stranger gọi service request_join → membership pending + boss nhận outbound</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -1461,56 +1493,24 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>outbound tới assignee DM + boss conv</t>
+          <t>membership status=pending + outbound to boss conv</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Test phần TRƯỚC của join flow</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Escalation</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Reminder fire 4h trước, target im lặng → _check_no_reply_reminders → bot DM boss</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>outbound nhắc boss về Long + escalated=1</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — _check_no_reply_reminders scheduler tick mới (30 phút) + outbound_messages.escalated column</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Task từ group, assignee chưa join → reminder vào group</t>
+          <t>Task overdue (DM context) → assignee DM + boss report</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group</t>
+          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>outbound vào source group</t>
+          <t>outbound tới assignee DM + boss conv</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -1555,52 +1555,136 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Reminder fire 4h trước, target im lặng → _check_no_reply_reminders → bot DM boss</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>outbound nhắc boss về Long + escalated=1</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — _check_no_reply_reminders scheduler tick mới (30 phút) + outbound_messages.escalated column</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Task từ group, assignee chưa join → reminder vào group</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>outbound vào source group</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Cross-channel isolation per boss</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Boss Zalo + Telegram-only assignee → reminder vào group, KHÔNG DM cross-channel</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Boss có primary_channel='zalo', assignee chỉ có Telegram identity → reminder PHẢI vào group, KHÔNG được DM Long qua Telegram</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>outbound vào group + KHÔNG outbound vào Long DM</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>FIXED — bosses.primary_channel column + is_target_on_boss_channel filter trong _resolve_task_targets</t>
         </is>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 15:43</t>
+          <t>2026-05-14 16:11</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Boss duyệt pending member</t>
+          <t>Boss duyệt + stranger được báo qua channel của họ</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Pre-insert pending membership → boss DM 'duyệt' → approve_join → membership active</t>
+          <t>Boss DM duyệt → approve_join → membership active + stranger nhận outbound qua channel của stranger</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>tool approve_join + membership.status='active'</t>
+          <t>approve_join + membership active + outbound vào stranger conv</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FIXED — approve_join notify stranger qua _messenger_for</t>
         </is>
       </c>
     </row>
@@ -1498,61 +1498,61 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Test phần TRƯỚC của join flow</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Onboard</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Hỏi boss / xin phép khi có người mới</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>O4</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Listing isolation: Zalo stranger không thấy boss Telegram</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>handle_join_inquiry từ Zalo conv: response KHÔNG chứa tên boss Telegram. Từ Telegram conv: response CÓ.</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Zalo listing không chứa 'Linh'; Telegram listing có 'Linh'</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — _filter_bosses_for_channel strict isolation: stranger Zalo không thể chọn boss Telegram ngay từ tầng listing. Bosses NULL primary_channel cũng bị hide.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Escalation</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Task overdue (DM context) → assignee DM + boss report</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>outbound tới assignee DM + boss conv</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
+          <t>Task overdue (DM context) → assignee DM + boss report</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Reminder fire 4h trước, target im lặng → _check_no_reply_reminders → bot DM boss</t>
+          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>outbound nhắc boss về Long + escalated=1</t>
+          <t>outbound tới assignee DM + boss conv</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>FIXED — _check_no_reply_reminders scheduler tick mới (30 phút) + outbound_messages.escalated column</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1609,82 +1609,124 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Reminder fire 4h trước, target im lặng → _check_no_reply_reminders → bot DM boss</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>outbound nhắc boss về Long + escalated=1</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — _check_no_reply_reminders scheduler tick mới (30 phút) + outbound_messages.escalated column</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Task từ group, assignee chưa join → reminder vào group</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>outbound vào source group</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Cross-channel isolation per boss</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Boss Zalo + Telegram-only assignee → reminder vào group, KHÔNG DM cross-channel</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Boss có primary_channel='zalo', assignee chỉ có Telegram identity → reminder PHẢI vào group, KHÔNG được DM Long qua Telegram</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>outbound vào group + KHÔNG outbound vào Long DM</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>FIXED — bosses.primary_channel column + is_target_on_boss_channel filter trong _resolve_task_targets</t>
         </is>

--- a/docs/self_test_clusters.xlsx
+++ b/docs/self_test_clusters.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -151,9 +151,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -527,17 +524,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="64" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -555,7 +550,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14 16:11</t>
+          <t>2026-05-14 16:30</t>
         </is>
       </c>
     </row>
@@ -630,35 +625,25 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>cluster_purpose</t>
+          <t>case_id</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>case_name</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>case_intent</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -672,39 +657,25 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
           <t>T1</t>
         </is>
       </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>DM tạo task — bot gọi create_task</t>
+        </is>
+      </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>DM tạo task</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Boss DM bot 'tạo task ...' → bot gọi create_task</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>tool create_task được gọi</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>create_task tool called</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -714,39 +685,25 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
           <t>T2</t>
         </is>
       </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>DM liệt kê task — bot gọi list_tasks</t>
+        </is>
+      </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>DM liệt kê task</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Boss DM 'cho xem danh sách task' → bot gọi list_tasks</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>tool list_tasks được gọi</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>list_tasks tool called</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -756,39 +713,25 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
           <t>T3a</t>
         </is>
       </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Group @mention giao task — Telegram assignee (id numeric)</t>
+        </is>
+      </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Group @mention giao task — Telegram assignee</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Trong group, boss @bot 'giao Long task' (Chat ID Telegram numeric) → resolve được id, create_task không crash</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>tool create_task không lỗi</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>create_task không lỗi</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -798,39 +741,25 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Boss tạo / liệt kê / cập nhật task qua DM hoặc group</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
           <t>T3b</t>
         </is>
       </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Group @mention giao task — Zalo assignee (id alphanum)</t>
+        </is>
+      </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Group @mention giao task — Zalo assignee</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Trong group, boss @bot 'giao Hùng task' (Chat ID Zalo alphanum) → resolve được id, create_task không crash</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>tool create_task không lỗi</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>create_task không lỗi</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -839,8 +768,6 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -850,39 +777,25 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Tạo / fire / nhận diện nguồn reminder</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
           <t>R1</t>
         </is>
       </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>DM self-reminder</t>
+        </is>
+      </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>DM: self-reminder</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Boss DM 'nhắc tôi ...' → tool create_reminder với target=boss</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>tool create_reminder được gọi</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>create_reminder called</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -892,39 +805,25 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Tạo / fire / nhận diện nguồn reminder</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
           <t>R2</t>
         </is>
       </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Group @mention nhắc 1 member</t>
+        </is>
+      </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Group @mention nhắc 1 member</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Trong group, boss @bot 'nhắc Long' → create_reminder với target=member, source_chat_id=group</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>tool create_reminder được gọi</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>create_reminder called với target + source_chat_id</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -934,37 +833,27 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Tạo / fire / nhận diện nguồn reminder</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
           <t>R3</t>
         </is>
       </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Fire reminder target + source group → 3 destinations</t>
+        </is>
+      </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Fire reminder có target + source group → 3 destinations</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>send_reminder(target_chat_id + source_chat_id) → target nhận DM + boss nhận cc + source group nhận public notice 'Vừa nhắc X: ...'</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>3 outbound: target DM, boss cc, source group</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — reminder_agent.send_reminder giờ post thêm notice vào source group khi reminder được tạo trong group context</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>target DM + boss cc + source group public notice</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>reminder_agent post thêm vào source_chat_id</t>
         </is>
       </c>
     </row>
@@ -976,39 +865,25 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Tạo / fire / nhận diện nguồn reminder</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
           <t>R4</t>
         </is>
       </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Fire reminder source-only (không target) → vào source group</t>
+        </is>
+      </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Fire reminder source-only</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Reminder không có target_chat_id, có source_chat_id → outbound vào source group thay vì DM boss</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>outbound vào source group</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1018,39 +893,25 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Tạo / fire / nhận diện nguồn reminder</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
           <t>R5</t>
         </is>
       </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Fire DM-only self-reminder → chỉ boss</t>
+        </is>
+      </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Fire DM-only self-reminder → chỉ boss</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Self-reminder trong DM (target=None, source=None) → fire chỉ DM boss; KHÔNG group, KHÔNG DM người khác</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>outbound chỉ tới boss conv</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>Đảm bảo nhắc lẻ không bị leak ra group / contact khác</t>
-        </is>
-      </c>
+      <c r="F19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1060,39 +921,25 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Tạo / fire / nhận diện nguồn reminder</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
           <t>R6</t>
         </is>
       </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Fire DM-only target reminder → DM target + boss, KHÔNG group</t>
+        </is>
+      </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Fire DM-only target reminder → DM target + boss, KHÔNG group</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Boss DM tạo reminder cho Long (target có, source=None) → fire DM Long + cc boss; group KHÔNG có post</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>outbound tới target DM + boss; group conv không có</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>Bảo đảm boss DM riêng → fire không lén post vào group</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>target DM + boss cc; group conv không có</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1101,8 +948,6 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -1112,39 +957,25 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Khả năng auto-take note từ hội thoại tự nhiên</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
           <t>N1</t>
         </is>
       </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Auto-append note khi boss chia sẻ context cá nhân</t>
+        </is>
+      </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Auto-append khi boss chia sẻ context cá nhân</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Boss nói 'gọi tôi là anh Đạt' → bot append_note / update_note</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>tool append_note / update_note được gọi</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>append_note / update_note called</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1153,8 +984,6 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1164,37 +993,27 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
           <t>F1</t>
         </is>
       </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>DM gửi file .txt + caption — bot đọc nội dung</t>
+        </is>
+      </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>DM gửi file text + caption</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Boss gửi .txt + 'tóm tắt' → bot phải đọc nội dung file (keyword đặc trưng zulipix/qorantek phải xuất hiện)</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>bot reference keyword zulipix/qorantek từ file</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — _ingest_text handler đọc text/plain (Zalo bridge thường drop mime)</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>reply reference keyword đặc trưng từ file</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>_ingest_text handler cho text/plain</t>
         </is>
       </c>
     </row>
@@ -1206,37 +1025,27 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
           <t>F2</t>
         </is>
       </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>DM paste link YouTube — bot fetch metadata + transcript</t>
+        </is>
+      </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>DM paste link YouTube</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Boss gửi YouTube link → bot fetch via oEmbed</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>tool fetch_url được gọi</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — fetch_url tool mới + url_fetch_service hit YouTube oEmbed</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>fetch_url called</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>fetch_url tool + url_fetch_service oEmbed + youtube-transcript-api</t>
         </is>
       </c>
     </row>
@@ -1248,37 +1057,27 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
           <t>F3</t>
         </is>
       </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>DM paste link TikTok — bot fetch oEmbed + yt-dlp metadata</t>
+        </is>
+      </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>DM paste link TikTok</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Boss gửi TikTok link → bot fetch via oEmbed</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>tool fetch_url được gọi</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — fetch_url tool</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>fetch_url called</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>fetch_url tool — caption/uploader/duration/views</t>
         </is>
       </c>
     </row>
@@ -1290,39 +1089,25 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
           <t>F4</t>
         </is>
       </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>DM paste link bài báo — bot fetch HTML summary</t>
+        </is>
+      </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>DM paste link bài báo (vnexpress)</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Boss gửi link tin tức → bot fetch HTML + summary</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>tool fetch_url được gọi</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>Path generic HTML qua fetch_url (trước đây dùng web_search; giờ chính xác hơn)</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>fetch_url called</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -1332,37 +1117,27 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Bot xử lý file đính kèm và link YouTube/TikTok/báo</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
           <t>F5</t>
         </is>
       </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Image attachment (PNG) — bot nhận diện ảnh</t>
+        </is>
+      </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Image attachment (PNG 32x32 đỏ)</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Boss gửi ảnh + 'trong ảnh này có gì' → bot ingest, reply nhắc ảnh/màu</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>reply nhắc tới ảnh / màu</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>File ingestion → LOCAL_IMAGE sentinel + OpenAI Vision</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>reply nhắc tới ảnh/màu</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>LOCAL_IMAGE sentinel + OpenAI Vision</t>
         </is>
       </c>
     </row>
@@ -1373,8 +1148,6 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1384,37 +1157,27 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
           <t>O1</t>
         </is>
       </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>New-member event trong group → bot proactive DM boss</t>
+        </is>
+      </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>New-member event trong group → bot phải hỏi boss</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Người mới vào group đã onboarded → bot proactive DM boss hỏi role</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>outbound tới boss có tên 'Người Mới'</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — _notify_boss_new_members trong secretary_agent.handle_message (qua _messenger_for nên route đúng channel boss)</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>outbound tới boss có tên người mới</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>_notify_boss_new_members route qua channel của boss</t>
         </is>
       </c>
     </row>
@@ -1426,37 +1189,27 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
           <t>O2</t>
         </is>
       </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Boss duyệt + stranger được báo qua channel của họ</t>
+        </is>
+      </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Boss duyệt + stranger được báo qua channel của họ</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Boss DM duyệt → approve_join → membership active + stranger nhận outbound qua channel của stranger</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>approve_join + membership active + outbound vào stranger conv</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — approve_join notify stranger qua _messenger_for</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>approve_join giờ notify stranger</t>
         </is>
       </c>
     </row>
@@ -1468,39 +1221,25 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
           <t>O3</t>
         </is>
       </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Stranger gọi request_join → pending row + boss DM</t>
+        </is>
+      </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Stranger gọi request_join → pending row + boss được DM</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Stranger gọi service request_join → membership pending + boss nhận outbound</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>membership status=pending + outbound to boss conv</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -1510,37 +1249,27 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Hỏi boss / xin phép khi có người mới</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
           <t>O4</t>
         </is>
       </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Listing isolation: Zalo stranger không thấy boss Telegram</t>
+        </is>
+      </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Listing isolation: Zalo stranger không thấy boss Telegram</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>handle_join_inquiry từ Zalo conv: response KHÔNG chứa tên boss Telegram. Từ Telegram conv: response CÓ.</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Zalo listing không chứa 'Linh'; Telegram listing có 'Linh'</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — _filter_bosses_for_channel strict isolation: stranger Zalo không thể chọn boss Telegram ngay từ tầng listing. Bosses NULL primary_channel cũng bị hide.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Zalo listing không chứa 'Linh'; Telegram listing có</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>_filter_bosses_for_channel strict — NULL primary_channel cũng hidden</t>
         </is>
       </c>
     </row>
@@ -1551,8 +1280,6 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -1562,39 +1289,25 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
           <t>E1</t>
         </is>
       </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Task overdue (DM context) → assignee DM + boss report</t>
+        </is>
+      </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Task overdue (DM context) → assignee DM + boss report</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Task không có Group ID + assignee có Chat ID → reminder DM tới assignee + boss nhận report</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>outbound tới assignee DM + boss conv</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -1604,37 +1317,27 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
           <t>E2</t>
         </is>
       </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Member nhắc deadline không reply → bot báo sếp</t>
+        </is>
+      </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Member bị nhắc deadline không reply → bot báo sếp</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Reminder fire 4h trước, target im lặng → _check_no_reply_reminders → bot DM boss</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>outbound nhắc boss về Long + escalated=1</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — _check_no_reply_reminders scheduler tick mới (30 phút) + outbound_messages.escalated column</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>outbound nhắc boss + escalated=1</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>_check_no_reply_reminders tick 30min + outbound_messages.escalated</t>
         </is>
       </c>
     </row>
@@ -1646,39 +1349,25 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Bot tự báo sếp / route reminder khi quá hạn</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
           <t>E3</t>
         </is>
       </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Task từ group, assignee chưa join → reminder vào group</t>
+        </is>
+      </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Task từ group, assignee chưa join → reminder vào group</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Task có Group ID + assignee không có Chat ID → reminder fallback vào group</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>outbound vào source group</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -1687,8 +1376,6 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -1698,43 +1385,33 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Cross-channel isolation per boss</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
           <t>C1</t>
         </is>
       </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Boss Zalo + Telegram-only assignee → reminder vào group, KHÔNG DM cross-channel</t>
+        </is>
+      </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Boss Zalo + Telegram-only assignee → reminder vào group, KHÔNG DM cross-channel</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Boss có primary_channel='zalo', assignee chỉ có Telegram identity → reminder PHẢI vào group, KHÔNG được DM Long qua Telegram</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>outbound vào group + KHÔNG outbound vào Long DM</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>FIXED — bosses.primary_channel column + is_target_on_boss_channel filter trong _resolve_task_targets</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>outbound vào group; KHÔNG outbound vào Long DM</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>bosses.primary_channel + is_target_on_boss_channel filter</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
